--- a/Dependencies/Ping_2018/fc/fragments_per_saap_4barplot_allDS.xlsx
+++ b/Dependencies/Ping_2018/fc/fragments_per_saap_4barplot_allDS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/Dependencies/Ping_2018/fc/fragments_per_saap_4barplot_allDS.xlsx
+++ b/Dependencies/Ping_2018/fc/fragments_per_saap_4barplot_allDS.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>287</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
